--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/2538-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/2538-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{49E14575-E4A3-4388-A4E4-22FB6392119D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2208152C-BBF8-40AA-92F3-9B44A946EC3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{4057D016-734E-4FF6-83A7-44A9C52A7DAD}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{FCB26F6C-06A1-4663-A361-16721148BA13}"/>
   </bookViews>
   <sheets>
     <sheet name="2538-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1571,25 +1571,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F30BB3F8-8751-4B01-9029-E8272E051B9F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96724B6E-7CAA-4BC3-A10D-C45044B60ED6}">
   <dimension ref="A1:X43"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="15" width="6.25" customWidth="1"/>
-    <col min="16" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1623,7 +1622,7 @@
       <c r="W1" s="30"/>
       <c r="X1" s="22"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1659,7 +1658,7 @@
       <c r="W2" s="32"/>
       <c r="X2" s="33"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1711,7 +1710,7 @@
       </c>
       <c r="X3" s="36"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1779,7 +1778,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="37">
         <v>2024</v>
       </c>
@@ -1851,7 +1850,7 @@
         <v>6.76</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="39">
         <v>2023</v>
       </c>
@@ -1923,7 +1922,7 @@
         <v>5.99</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="41"/>
       <c r="B7" s="42"/>
       <c r="C7" s="17" t="s">
@@ -1951,7 +1950,7 @@
       <c r="W7" s="48"/>
       <c r="X7" s="44"/>
     </row>
-    <row r="8" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="37">
         <v>2022</v>
       </c>
@@ -2023,7 +2022,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="49">
         <v>2021</v>
       </c>
@@ -2095,7 +2094,7 @@
         <v>4.63</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="37">
         <v>2020</v>
       </c>
@@ -2167,7 +2166,7 @@
         <v>5.43</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="49">
         <v>2019</v>
       </c>
@@ -2239,7 +2238,7 @@
         <v>6.54</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="37">
         <v>2018</v>
       </c>
@@ -2311,7 +2310,7 @@
         <v>5.38</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="49">
         <v>2017</v>
       </c>
@@ -2383,7 +2382,7 @@
         <v>8.16</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="37">
         <v>2016</v>
       </c>
@@ -2455,7 +2454,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="49">
         <v>2015</v>
       </c>
@@ -2527,7 +2526,7 @@
         <v>15.9</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="37">
         <v>2014</v>
       </c>
@@ -2599,7 +2598,7 @@
         <v>8.77</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="49">
         <v>2013</v>
       </c>
@@ -2671,7 +2670,7 @@
         <v>10.3</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="37">
         <v>2012</v>
       </c>
@@ -2743,7 +2742,7 @@
         <v>7.45</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="49">
         <v>2011</v>
       </c>
@@ -2815,7 +2814,7 @@
         <v>10.6</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="51">
         <v>2010</v>
       </c>
@@ -2887,7 +2886,7 @@
         <v>10.3</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="53"/>
       <c r="B21" s="54"/>
       <c r="C21" s="20" t="s">
@@ -2915,7 +2914,7 @@
       <c r="W21" s="60"/>
       <c r="X21" s="56"/>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="39">
         <v>2009</v>
       </c>
@@ -2987,7 +2986,7 @@
         <v>8.92</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="41"/>
       <c r="B23" s="42"/>
       <c r="C23" s="17" t="s">
@@ -3015,7 +3014,7 @@
       <c r="W23" s="48"/>
       <c r="X23" s="44"/>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="51">
         <v>2008</v>
       </c>
@@ -3087,7 +3086,7 @@
         <v>19.899999999999999</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="53"/>
       <c r="B25" s="54"/>
       <c r="C25" s="20" t="s">
@@ -3115,7 +3114,7 @@
       <c r="W25" s="60"/>
       <c r="X25" s="56"/>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="49">
         <v>2007</v>
       </c>
@@ -3187,7 +3186,7 @@
         <v>26.3</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="37">
         <v>2006</v>
       </c>
@@ -3259,7 +3258,7 @@
         <v>6.81</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="49">
         <v>2005</v>
       </c>
@@ -3331,7 +3330,7 @@
         <v>14.9</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="37">
         <v>2004</v>
       </c>
@@ -3403,7 +3402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="49">
         <v>2003</v>
       </c>
@@ -3475,7 +3474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="37">
         <v>2002</v>
       </c>
@@ -3547,7 +3546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="49">
         <v>2001</v>
       </c>
@@ -3619,7 +3618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="37">
         <v>2000</v>
       </c>
@@ -3691,7 +3690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="49">
         <v>1999</v>
       </c>
@@ -3763,7 +3762,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="51">
         <v>1998</v>
       </c>
@@ -3835,7 +3834,7 @@
         <v>17.100000000000001</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="53"/>
       <c r="B36" s="54"/>
       <c r="C36" s="20" t="s">
@@ -3863,7 +3862,7 @@
       <c r="W36" s="60"/>
       <c r="X36" s="56"/>
     </row>
-    <row r="37" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="49">
         <v>1997</v>
       </c>
@@ -3935,7 +3934,7 @@
         <v>15.2</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="37">
         <v>1996</v>
       </c>
@@ -4007,7 +4006,7 @@
         <v>7.18</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="49">
         <v>1995</v>
       </c>
@@ -4079,7 +4078,7 @@
         <v>3.08</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="37">
         <v>1994</v>
       </c>
@@ -4151,7 +4150,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="49">
         <v>1993</v>
       </c>
@@ -4223,7 +4222,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="37">
         <v>1992</v>
       </c>
@@ -4295,7 +4294,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="49" t="s">
         <v>59</v>
       </c>
